--- a/intake_forms/016_medical_induction_information_form--intake_forms.xlsx
+++ b/intake_forms/016_medical_induction_information_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new_patient',_'label':_'new_patient'}</t>
+          <t>new_patient</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'New Patient', 'label': 'New Patient'}</t>
+          <t>New Patient</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'follow-up',_'label':_'follow-up'}</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Follow-up', 'label': 'Follow-up'}</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sms',_'label':_'sms'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'SMS', 'label': 'SMS'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spouse',_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spouse', 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'child',_'label':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Child', 'label': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
